--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:21:01+00:00</t>
+    <t>2026-07-23T23:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:35:23+00:00</t>
+    <t>2026-07-23T23:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:49:03+00:00</t>
+    <t>2026-07-25T21:53:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T21:53:45+00:00</t>
+    <t>2026-07-25T22:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:03:00+00:00</t>
+    <t>2026-07-25T22:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:20:35+00:00</t>
+    <t>2026-07-25T22:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -24,13 +24,13 @@
     <t>ID</t>
   </si>
   <si>
-    <t>selftest-model</t>
+    <t>preview-model</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/forschungsgruppe-digital-health/ig-template-mii-kds/StructureDefinition/selftest-model</t>
+    <t>https://github.com/medizininformatik-initiative/ig-template-mii-kds/StructureDefinition/preview-model</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,13 +42,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>SelfTestModel</t>
+    <t>PreviewModel</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Self-Test Model</t>
+    <t>Preview Model</t>
   </si>
   <si>
     <t>Status</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:27:53+00:00</t>
+    <t>2026-07-26T06:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Forschungsgruppe Digital Health, TU Dresden (https://github.com/forschungsgruppe-digital-health)</t>
+    <t>Forschungsgruppe Digital Health, TU Dresden (https://github.com/medizininformatik-initiative)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Minimal logical model that exists only so the template self-test IG builds and its artifact layout renders; not an MII artifact.</t>
+    <t>Minimal logical model that exists only so the template preview IG builds and its artifact layout renders; not an MII artifact.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -253,7 +253,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>selftest-model.placeholder</t>
+    <t>preview-model.placeholder</t>
   </si>
   <si>
     <t>1</t>
@@ -576,9 +576,9 @@
   <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.15234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.8828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.8828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="12.5859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.3203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="22.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="7.6796875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -608,7 +608,7 @@
     <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="21.8828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="22.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.046875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,19 +63,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:58:13+00:00</t>
+    <t>2026-07-26T07:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Forschungsgruppe Digital Health, TU Dresden</t>
+    <t>Medical Informatics Initiative (MII)</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Forschungsgruppe Digital Health, TU Dresden (https://github.com/medizininformatik-initiative)</t>
+    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de/en)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T07:51:37+00:00</t>
+    <t>2026-07-26T09:04:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T09:04:46+00:00</t>
+    <t>2026-07-26T10:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:03:38+00:00</t>
+    <t>2026-07-26T10:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:40:12+00:00</t>
+    <t>2026-07-26T12:57:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:57:49+00:00</t>
+    <t>2026-07-26T14:55:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:55:55+00:00</t>
+    <t>2026-07-26T18:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:22:21+00:00</t>
+    <t>2026-07-26T18:37:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:37:19+00:00</t>
+    <t>2026-07-27T01:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T01:54:07+00:00</t>
+    <t>2026-07-27T07:17:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:17:22+00:00</t>
+    <t>2026-07-27T07:54:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:54:11+00:00</t>
+    <t>2026-07-27T10:27:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:16+00:00</t>
+    <t>2026-07-27T10:48:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:48:46+00:00</t>
+    <t>2026-07-29T19:15:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T19:15:27+00:00</t>
+    <t>2026-07-29T19:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T19:24:20+00:00</t>
+    <t>2026-07-30T03:36:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T03:36:15+00:00</t>
+    <t>2026-07-30T09:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:38:09+00:00</t>
+    <t>2026-07-30T13:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:08:53+00:00</t>
+    <t>2026-07-30T14:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:25:11+00:00</t>
+    <t>2026-07-30T15:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:32:03+00:00</t>
+    <t>2026-07-30T15:45:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:45:53+00:00</t>
+    <t>2026-07-30T16:02:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de/en)</t>
+    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T16:02:24+00:00</t>
+    <t>2026-07-30T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T16:16:41+00:00</t>
+    <t>2026-07-30T18:59:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T18:59:10+00:00</t>
+    <t>2026-07-30T19:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T19:38:20+00:00</t>
+    <t>2026-08-05T20:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T20:55:41+00:00</t>
+    <t>2026-08-06T07:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T07:53:42+00:00</t>
+    <t>2026-08-06T07:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T07:56:58+00:00</t>
+    <t>2026-08-06T10:03:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:03:31+00:00</t>
+    <t>2026-08-06T10:09:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:09:00+00:00</t>
+    <t>2026-08-06T11:57:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T11:57:56+00:00</t>
+    <t>2026-08-07T05:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T05:28:34+00:00</t>
+    <t>2026-08-07T05:30:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T05:30:56+00:00</t>
+    <t>2026-08-07T06:47:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T06:47:02+00:00</t>
+    <t>2026-08-13T13:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:38+00:00</t>
+    <t>2026-08-13T18:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T18:55:22+00:00</t>
+    <t>2026-08-13T18:58:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T18:58:29+00:00</t>
+    <t>2026-08-13T19:07:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T19:07:02+00:00</t>
+    <t>2026-08-13T19:49:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T19:49:24+00:00</t>
+    <t>2026-08-14T02:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:21:10+00:00</t>
+    <t>2026-08-14T02:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:33:29+00:00</t>
+    <t>2026-08-14T02:42:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:42:18+00:00</t>
+    <t>2026-08-14T02:44:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:44:34+00:00</t>
+    <t>2026-08-14T05:24:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:24:23+00:00</t>
+    <t>2026-08-14T05:30:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:30:00+00:00</t>
+    <t>2026-08-14T05:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,19 +63,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:32:39+00:00</t>
+    <t>2026-08-14T07:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII)</t>
+    <t>NUM-DIZ</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de)</t>
+    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T07:41:45+00:00</t>
+    <t>2026-08-14T09:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T09:31:44+00:00</t>
+    <t>2026-08-14T09:37:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T09:37:55+00:00</t>
+    <t>2026-08-14T10:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T10:56:11+00:00</t>
+    <t>2026-08-14T11:01:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T11:01:32+00:00</t>
+    <t>2026-08-15T21:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T21:47:27+00:00</t>
+    <t>2026-08-16T07:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T07:21:10+00:00</t>
+    <t>2026-08-16T09:05:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T09:05:44+00:00</t>
+    <t>2026-08-16T09:28:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T09:28:53+00:00</t>
+    <t>2026-08-16T09:57:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T09:57:47+00:00</t>
+    <t>2026-08-16T11:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T11:14:27+00:00</t>
+    <t>2026-08-16T11:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T11:42:03+00:00</t>
+    <t>2026-08-16T11:56:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T11:56:52+00:00</t>
+    <t>2026-08-16T12:16:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:16:10+00:00</t>
+    <t>2026-08-16T12:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:23:35+00:00</t>
+    <t>2026-08-16T12:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:28:32+00:00</t>
+    <t>2026-08-16T14:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T14:04:34+00:00</t>
+    <t>2026-08-17T19:19:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T19:19:47+00:00</t>
+    <t>2026-08-17T19:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T19:47:59+00:00</t>
+    <t>2026-08-17T19:59:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T19:59:03+00:00</t>
+    <t>2026-08-19T15:30:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T15:30:05+00:00</t>
+    <t>2026-08-19T17:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:39:50+00:00</t>
+    <t>2026-08-19T20:24:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T20:24:49+00:00</t>
+    <t>2026-08-20T09:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:48:22+00:00</t>
+    <t>2026-08-20T09:53:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
